--- a/stories/arbres/TREE-AUT-008.xlsx
+++ b/stories/arbres/TREE-AUT-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est à la maison avec papa. Bientôt on part. Hugo reprend ses affaires. Le seau. Le manteau. Le doudou. Il les reprend avant de partir. Maman appelle près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la cuisine. Une feuille tombe. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Papa dit : bravo.</t>
+          <t>Hugo va vers la cuisine. Une feuille tombe. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Bravo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. Une feuille tombe. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir.
+papa|Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un petit bruit d'eau. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Les chaussures font toc toc. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un vélo passe au loin. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Les chaussures font toc toc. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un vélo passe au loin. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. La lumière est claire. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un vélo passe au loin. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. La lumière est claire. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Ça sent le pain. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le jardin. Le vent est doux. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Papa dit : bravo.</t>
+          <t>Hugo va vers le jardin. Le vent est doux. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Bravo.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. Le vent est doux. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir.
+papa|Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6655,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6828,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Les chaussures font toc toc. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un vélo passe au loin. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. La lumière est claire. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un vélo passe au loin. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. La lumière est claire. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Ça sent le pain. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. La lumière est claire. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Ça sent le pain. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un chat miaule une fois. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. On entend un oiseau. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Papa dit : bravo.</t>
+          <t>Hugo va vers la chambre. On entend un oiseau. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Bravo.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. On entend un oiseau. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir.
+papa|Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11452,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11625,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un vélo passe au loin. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. La lumière est claire. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Ça sent le pain. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. La lumière est claire. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Ça sent le pain. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un chat miaule une fois. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Ça sent le pain. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un chat miaule une fois. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Une feuille tombe. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-008.xlsx
+++ b/stories/arbres/TREE-AUT-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Hugo est à la maison avec papa. Bientôt on part. Hugo reprend ses affaires. Le seau. Le manteau. Le doudou. Il les reprend avant de partir. Maman appelle près de la porte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Bravo.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|C'est le matin. Un petit bruit d'eau. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|C'est après la sieste. Les chaussures font toc toc. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|C'est le soir. Un vélo passe au loin. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|C'est le matin. Les chaussures font toc toc. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|C'est après la sieste. Un vélo passe au loin. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|C'est le soir. La lumière est claire. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|C'est le matin. Un vélo passe au loin. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|C'est après la sieste. La lumière est claire. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|C'est le soir. Ça sent le pain. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Bravo.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6662,6 +6698,7 @@
           <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6833,6 +6870,7 @@
           <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|C'est le matin. Les chaussures font toc toc. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|C'est après la sieste. Un vélo passe au loin. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|C'est le soir. La lumière est claire. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|C'est le matin. Un vélo passe au loin. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|C'est après la sieste. La lumière est claire. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|C'est le soir. Ça sent le pain. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|C'est le matin. La lumière est claire. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|C'est après la sieste. Ça sent le pain. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|C'est le soir. Un chat miaule une fois. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Bravo.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11459,6 +11523,7 @@
           <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11630,6 +11695,7 @@
           <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|C'est le matin. Un vélo passe au loin. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|C'est après la sieste. La lumière est claire. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|C'est le soir. Ça sent le pain. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|C'est le matin. La lumière est claire. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|C'est après la sieste. Ça sent le pain. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|C'est le soir. Un chat miaule une fois. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|C'est le matin. Ça sent le pain. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|C'est après la sieste. Un chat miaule une fois. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|C'est le soir. Une feuille tombe. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-008.xlsx
+++ b/stories/arbres/TREE-AUT-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — à la maison</t>
+          <t>Le seau jaune d'Aniss</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie s'est arrêtée. Aniss a joué. Bientôt on part. Il cherche le seau, le manteau et le doudou. Il reprend ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est à la maison avec papa. Bientôt on part. Hugo reprend ses affaires. Le seau. Le manteau. Le doudou. Il les reprend avant de partir. Maman appelle près de la porte.</t>
+          <t>La pluie vient de s'arrêter. La cour brille comme un miroir. Des feuilles mouillées collent à la fenêtre. Une goutte tombe de la gouttière. Ça fait toc. Près de la porte, un bol en terre. Les clés de papa tintent dedans. Les clés sont là. Un seau jaune attend près du paillasson. Un manteau bleu pend au crochet. Le doudou gris est sur le canapé. Aniss, on va bientôt partir. Aniss a joué dans la maison. Ses affaires sont un peu partout. J'arrive, maman. On reprend tes affaires. Avant de partir. Aniss regarde le seau. Il regarde le manteau. Il regarde le doudou. Tu les prends avec toi. En ce moment, Aniss se met à chercher. Tu as fini de jouer ? Oui, papa. Alors on cherche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,31 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est à la maison avec papa. Bientôt on part. Hugo reprend ses affaires. Le seau. Le manteau. Le doudou. Il les reprend avant de partir. Maman appelle près de la porte.</t>
+          <t>narrateur|La pluie vient de s'arrêter.
+narrateur|La cour brille comme un miroir.
+narrateur|Des feuilles mouillées collent à la fenêtre.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Ça fait toc.
+narrateur|Près de la porte, un bol en terre.
+narrateur|Les clés de papa tintent dedans.
+papa|Les clés sont là.
+narrateur|Un seau jaune attend près du paillasson.
+narrateur|Un manteau bleu pend au crochet.
+narrateur|Le doudou gris est sur le canapé.
+maman|Aniss, on va bientôt partir.
+narrateur|Aniss a joué dans la maison.
+narrateur|Ses affaires sont un peu partout.
+enfant-m|J'arrive, maman.
+papa|On reprend tes affaires.
+papa|Avant de partir.
+narrateur|Aniss regarde le seau.
+narrateur|Il regarde le manteau.
+narrateur|Il regarde le doudou.
+maman|Tu les prends avec toi.
+narrateur|En ce moment, Aniss se met à chercher.
+papa|Tu as fini de jouer ?
+enfant-m|Oui, papa.
+maman|Alors on cherche.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1389,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Aniss peut chercher dans la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1553,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Aniss peut chercher dans la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la cuisine. Une feuille tombe. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Bravo.</t>
+          <t>Aniss va vers la cuisine. Une feuille sèche tombe de la table. Ça sent encore le pain. Il cherche sous la table. Il cherche près des chaises. Le seau, papa ? Oui. On reprend tes affaires. Le seau. Le manteau. Avant de partir. Aniss trouve le seau près du buffet. Il le prend. Bravo, Aniss. Tu as cherché. Le manteau aussi, tout à l'heure. Aniss tient le seau. Je le tiens.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,8 +1721,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers la cuisine. Une feuille tombe. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir.
-papa|Bravo.</t>
+          <t>narrateur|Aniss va vers la cuisine.
+narrateur|Une feuille sèche tombe de la table.
+narrateur|Ça sent encore le pain.
+narrateur|Il cherche sous la table.
+narrateur|Il cherche près des chaises.
+enfant-m|Le seau, papa ?
+papa|Oui.
+papa|On reprend tes affaires.
+papa|Le seau.
+papa|Le manteau.
+papa|Avant de partir.
+narrateur|Aniss trouve le seau près du buffet.
+narrateur|Il le prend.
+maman|Bravo, Aniss.
+maman|Tu as cherché.
+papa|Le manteau aussi, tout à l'heure.
+narrateur|Aniss tient le seau.
+enfant-m|Je le tiens.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bientôt on part. Hugo fait quoi ?</t>
+          <t>Bientôt on part. Aniss fait quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1922,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
+          <t>narrateur|Bientôt on part.
+narrateur|Aniss fait quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+          <t>Oui. Aniss reprend ses affaires. Avant de partir. Il a cherché dans la cuisine. Il a pris le seau. Bravo. Tu as fait du bon travail. On continue ? Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2095,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+          <t>narrateur|Oui.
+papa|Aniss reprend ses affaires.
+maman|Avant de partir.
+narrateur|Il a cherché dans la cuisine.
+narrateur|Il a pris le seau.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|On continue ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2131,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Près des cubes, du livre, ou de la dînette ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2299,7 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Près des cubes, du livre, ou de la dînette ?</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2327,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans la cuisine, Aniss s'approche des cubes. Une petite tour est encore debout. On entend un oiseau. Près des cubes, il trouve encore une affaire. Encore une, papa. Oui. On reprend tes affaires. Avant de partir. Aniss met l'affaire avec le seau. Bravo. Tu cherches bien. Les cubes restent sur le tapis de la cuisine.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,7 +2467,18 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, Aniss s'approche des cubes.
+narrateur|Une petite tour est encore debout.
+narrateur|On entend un oiseau.
+narrateur|Près des cubes, il trouve encore une affaire.
+enfant-m|Encore une, papa.
+papa|Oui.
+papa|On reprend tes affaires.
+maman|Avant de partir.
+narrateur|Aniss met l'affaire avec le seau.
+papa|Bravo.
+papa|Tu cherches bien.
+narrateur|Les cubes restent sur le tapis de la cuisine.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2434,7 +2506,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2670,7 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2698,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Un petit bruit d'eau. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Un petit bruit d'eau dans l'évier. Dans la cuisine, près de les cubes, Aniss cherche. Sous la table, le seau jaune attend. J'ai le seau, papa. Tu reprends le seau. Bravo. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le seau est dans sa main.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2838,24 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Un petit bruit d'eau. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Un petit bruit d'eau dans l'évier.
+narrateur|Dans la cuisine, près de les cubes, Aniss cherche.
+narrateur|Sous la table, le seau jaune attend.
+enfant-m|J'ai le seau, papa.
+papa|Tu reprends le seau.
+papa|Bravo.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le seau est dans sa main.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2883,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de les cubes. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le seau est dans sa main. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3023,19 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de les cubes.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le seau est dans sa main.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3063,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les chaussures font toc toc. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Les chaussures font toc toc. Dans la cuisine, près de les cubes, Aniss cherche. Sur la chaise, le manteau bleu est plié. J'ai le manteau, maman. Tu reprends le manteau. Bravo. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le manteau est sur ses épaules.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3203,24 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Les chaussures font toc toc. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Les chaussures font toc toc.
+narrateur|Dans la cuisine, près de les cubes, Aniss cherche.
+narrateur|Sur la chaise, le manteau bleu est plié.
+enfant-m|J'ai le manteau, maman.
+maman|Tu reprends le manteau.
+maman|Bravo.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le manteau est sur ses épaules.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3248,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de les cubes. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le manteau est sur ses épaules. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3388,19 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de les cubes.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le manteau est sur ses épaules.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3428,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Un vélo passe au loin. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. Un vélo passe tout au loin. Dans la cuisine, près de les cubes, Aniss cherche. Contre le coussin, le doudou gris dort. J'ai le doudou. Tu reprends le doudou. Bravo. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le doudou est contre lui.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3568,24 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Un vélo passe au loin. Dans la cuisine, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|Un vélo passe tout au loin.
+narrateur|Dans la cuisine, près de les cubes, Aniss cherche.
+narrateur|Contre le coussin, le doudou gris dort.
+enfant-m|J'ai le doudou.
+papa|Tu reprends le doudou.
+papa|Bravo.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le doudou est contre lui.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3613,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de les cubes. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le doudou est contre lui. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3753,19 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de les cubes.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le doudou est contre lui.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3793,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans la cuisine, Aniss s'approche du livre. Le livre est ouvert sur la table. Ça sent l'herbe coupée par la fenêtre. Près du livre, il trouve encore une affaire. C'est le manteau ? Si c'est le manteau, tu le prends. On reprend tes affaires. Avant de partir. Aniss prend l'affaire. Bravo. Le livre reste sur la table.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,7 +3933,17 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, Aniss s'approche du livre.
+narrateur|Le livre est ouvert sur la table.
+narrateur|Ça sent l'herbe coupée par la fenêtre.
+narrateur|Près du livre, il trouve encore une affaire.
+enfant-m|C'est le manteau ?
+maman|Si c'est le manteau, tu le prends.
+papa|On reprend tes affaires.
+papa|Avant de partir.
+narrateur|Aniss prend l'affaire.
+papa|Bravo.
+narrateur|Le livre reste sur la table.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3802,7 +3971,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3966,7 +4135,7 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3994,7 +4163,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Les chaussures font toc toc. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Une feuille sèche glisse au sol. Dans la cuisine, près de le livre, Aniss cherche. Derrière les cubes, le seau dépasse. Le seau était sous la table. Cherche encore. Tu as le seau. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Les cubes restent sages.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4134,7 +4303,24 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Les chaussures font toc toc. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Une feuille sèche glisse au sol.
+narrateur|Dans la cuisine, près de le livre, Aniss cherche.
+narrateur|Derrière les cubes, le seau dépasse.
+enfant-m|Le seau était sous la table.
+maman|Cherche encore.
+maman|Tu as le seau.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Les cubes restent sages.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4162,7 +4348,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de le livre. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Les cubes restent sages. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4302,7 +4488,19 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de le livre.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Les cubes restent sages.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4330,7 +4528,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Un vélo passe au loin. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Ça sent l'herbe coupée. Dans la cuisine, près de le livre, Aniss cherche. Sur le dossier, le manteau pend. Le manteau était sur la chaise. Le manteau, tu le prends. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le livre reste ouvert un peu.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4470,7 +4668,23 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Un vélo passe au loin. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Dans la cuisine, près de le livre, Aniss cherche.
+narrateur|Sur le dossier, le manteau pend.
+enfant-m|Le manteau était sur la chaise.
+papa|Le manteau, tu le prends.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le livre reste ouvert un peu.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4498,7 +4712,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de le livre. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le livre reste ouvert un peu. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4638,7 +4852,19 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de le livre.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le livre reste ouvert un peu.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4666,7 +4892,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lumière est claire. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. La lumière est claire sur la table. Dans la cuisine, près de le livre, Aniss cherche. Entre deux cubes, le doudou est coincé. Le doudou était là. Le doudou aussi, avant de partir. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. La dînette ne part pas.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4806,7 +5032,23 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. La lumière est claire. Dans la cuisine, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|La lumière est claire sur la table.
+narrateur|Dans la cuisine, près de le livre, Aniss cherche.
+narrateur|Entre deux cubes, le doudou est coincé.
+enfant-m|Le doudou était là.
+maman|Le doudou aussi, avant de partir.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|La dînette ne part pas.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4834,7 +5076,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de le livre. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. La dînette ne part pas. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4974,7 +5216,19 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de le livre.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|La dînette ne part pas.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5002,7 +5256,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans la cuisine, Aniss s'approche de la dînette. Deux tasses sont encore en rond. Le soleil chauffe un peu le carreau. Près de la dînette, il trouve encore une affaire. Le doudou était là. Tu le prends. Avant de partir. On reprend tes affaires. Aniss serre l'affaire. Bravo. Tu as cherché. La dînette reste sage.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5142,7 +5396,18 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la cuisine, Aniss s'approche de la dînette.
+narrateur|Deux tasses sont encore en rond.
+narrateur|Le soleil chauffe un peu le carreau.
+narrateur|Près de la dînette, il trouve encore une affaire.
+enfant-m|Le doudou était là.
+maman|Tu le prends.
+maman|Avant de partir.
+papa|On reprend tes affaires.
+narrateur|Aniss serre l'affaire.
+maman|Bravo.
+maman|Tu as cherché.
+narrateur|La dînette reste sage.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5170,7 +5435,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5334,7 +5599,7 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5362,7 +5627,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Un vélo passe au loin. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Le soleil chauffe un peu le carreau. Dans la cuisine, près de la dînette, Aniss cherche. Près de l'évier, le seau est posé. Je le prends. Tu as repris une affaire. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. L'évier ne coule plus.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5502,7 +5767,23 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Un vélo passe au loin. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Le soleil chauffe un peu le carreau.
+narrateur|Dans la cuisine, près de la dînette, Aniss cherche.
+narrateur|Près de l'évier, le seau est posé.
+enfant-m|Je le prends.
+papa|Tu as repris une affaire.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'évier ne coule plus.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5530,7 +5811,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de la dînette. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. L'évier ne coule plus. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5670,7 +5951,19 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de la dînette.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'évier ne coule plus.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5698,7 +5991,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La lumière est claire. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Ça sent le pain encore chaud. Dans la cuisine, près de la dînette, Aniss cherche. Au crochet de la cuisine, le manteau. Il est à moi. On les prend toutes. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le crochet est vide.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5838,7 +6131,23 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. La lumière est claire. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Ça sent le pain encore chaud.
+narrateur|Dans la cuisine, près de la dînette, Aniss cherche.
+narrateur|Au crochet de la cuisine, le manteau.
+enfant-m|Il est à moi.
+maman|On les prend toutes.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le crochet est vide.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5866,7 +6175,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de la dînette. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le crochet est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6006,7 +6315,19 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de la dînette.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le crochet est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6034,7 +6355,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Ça sent le pain. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. Un chat miaule une seule fois. Dans la cuisine, près de la dînette, Aniss cherche. Dans le panier, le doudou est roulé. Je l'ai trouvé. Avant de partir, tu les as. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le panier est vide.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6174,7 +6495,23 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Ça sent le pain. Dans la cuisine, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|Un chat miaule une seule fois.
+narrateur|Dans la cuisine, près de la dînette, Aniss cherche.
+narrateur|Dans le panier, le doudou est roulé.
+enfant-m|Je l'ai trouvé.
+papa|Avant de partir, tu les as.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le panier est vide.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6202,7 +6539,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la cuisine. Près de la dînette. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le panier est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6342,7 +6679,19 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la cuisine.
+narrateur|Près de la dînette.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le panier est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6370,7 +6719,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le jardin. Le vent est doux. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Bravo.</t>
+          <t>Aniss va vers le jardin. Le vent est doux sur les joues. L'herbe est encore mouillée. Il cherche près du banc. Il cherche près des pots. Le manteau, maman ? Oui. On reprend tes affaires. Le seau. Le manteau. Avant de partir. Aniss voit le manteau sur le banc. Il le prend. Bravo, Aniss. Tu as cherché. Le seau aussi, tout à l'heure. Aniss tient le manteau. Il est un peu humide. C'est bien. Tu l'as.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6510,8 +6859,26 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers le jardin. Le vent est doux. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir.
-papa|Bravo.</t>
+          <t>narrateur|Aniss va vers le jardin.
+narrateur|Le vent est doux sur les joues.
+narrateur|L'herbe est encore mouillée.
+narrateur|Il cherche près du banc.
+narrateur|Il cherche près des pots.
+enfant-m|Le manteau, maman ?
+maman|Oui.
+maman|On reprend tes affaires.
+papa|Le seau.
+papa|Le manteau.
+papa|Avant de partir.
+narrateur|Aniss voit le manteau sur le banc.
+narrateur|Il le prend.
+papa|Bravo, Aniss.
+papa|Tu as cherché.
+maman|Le seau aussi, tout à l'heure.
+narrateur|Aniss tient le manteau.
+enfant-m|Il est un peu humide.
+maman|C'est bien.
+maman|Tu l'as.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6539,7 +6906,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bientôt on part. Hugo fait quoi ?</t>
+          <t>Bientôt on part. Aniss fait quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6695,7 +7062,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
+          <t>narrateur|Bientôt on part.
+narrateur|Aniss fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6723,7 +7091,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+          <t>Oui. Aniss reprend ses affaires. Avant de partir. Il a cherché dans le jardin. Il a pris le manteau. Bravo. On continue ensemble. D'accord.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6867,7 +7235,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+          <t>narrateur|Oui.
+papa|Aniss reprend ses affaires.
+maman|Avant de partir.
+narrateur|Il a cherché dans le jardin.
+narrateur|Il a pris le manteau.
+papa|Bravo.
+papa|On continue ensemble.
+enfant-m|D'accord.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6895,7 +7270,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Près des cubes, du livre, ou de la dînette ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7063,7 +7438,7 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Près des cubes, du livre, ou de la dînette ?</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7091,7 +7466,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans le jardin, Aniss s'approche des cubes. Les cubes sont mouillés un peu. On entend un oiseau. Près des cubes, il trouve encore une affaire. Je la prends. Oui. On reprend tes affaires. Avant de partir. Aniss essuie un peu l'affaire. Bravo. Les cubes restent dans l'herbe.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7231,7 +7606,17 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, Aniss s'approche des cubes.
+narrateur|Les cubes sont mouillés un peu.
+narrateur|On entend un oiseau.
+narrateur|Près des cubes, il trouve encore une affaire.
+enfant-m|Je la prends.
+papa|Oui.
+papa|On reprend tes affaires.
+maman|Avant de partir.
+narrateur|Aniss essuie un peu l'affaire.
+papa|Bravo.
+narrateur|Les cubes restent dans l'herbe.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7259,7 +7644,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7423,7 +7808,7 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7451,7 +7836,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Les chaussures font toc toc. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Une goutte tombe de la gouttière. Dans le jardin, près de les cubes, Aniss cherche. Dans l'herbe, le seau a un peu d'eau. Il y a un peu d'eau. Verse l'eau. Puis tu prends le seau. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. L'herbe ne tient plus le seau.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7591,7 +7976,24 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Les chaussures font toc toc. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Dans le jardin, près de les cubes, Aniss cherche.
+narrateur|Dans l'herbe, le seau a un peu d'eau.
+enfant-m|Il y a un peu d'eau.
+maman|Verse l'eau.
+maman|Puis tu prends le seau.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|L'herbe ne tient plus le seau.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7619,7 +8021,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de les cubes. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. L'herbe ne tient plus le seau. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7759,7 +8161,19 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de les cubes.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'herbe ne tient plus le seau.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7787,7 +8201,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Un vélo passe au loin. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Le store claque tout doux. Dans le jardin, près de les cubes, Aniss cherche. Sur le banc, le manteau est plié. Il est plié. Le manteau, tu le mets. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le banc est vide.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7927,7 +8341,23 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Un vélo passe au loin. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Le store claque tout doux.
+narrateur|Dans le jardin, près de les cubes, Aniss cherche.
+narrateur|Sur le banc, le manteau est plié.
+enfant-m|Il est plié.
+papa|Le manteau, tu le mets.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le banc est vide.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7955,7 +8385,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de les cubes. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le banc est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8095,7 +8525,19 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de les cubes.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le banc est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8123,7 +8565,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lumière est claire. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. Un oiseau répond dehors. Dans le jardin, près de les cubes, Aniss cherche. Sous le banc, le doudou attend. Il est sous le banc. Le doudou, tu le serres. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le dessous du banc est vide.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8263,7 +8705,23 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. La lumière est claire. Dans le jardin, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|Un oiseau répond dehors.
+narrateur|Dans le jardin, près de les cubes, Aniss cherche.
+narrateur|Sous le banc, le doudou attend.
+enfant-m|Il est sous le banc.
+maman|Le doudou, tu le serres.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le dessous du banc est vide.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8291,7 +8749,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de les cubes. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le dessous du banc est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8431,7 +8889,19 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de les cubes.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le dessous du banc est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8459,7 +8929,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans le jardin, Aniss s'approche du livre. Le livre est sous le banc, au sec. Ça sent l'herbe coupée. Près du livre, il trouve encore une affaire. Elle était cachée. Tu la prends. Avant de partir. On reprend tes affaires. Aniss prend l'affaire. Bravo. Tu as cherché. Le livre reste sous le banc.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8599,7 +9069,18 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, Aniss s'approche du livre.
+narrateur|Le livre est sous le banc, au sec.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Près du livre, il trouve encore une affaire.
+enfant-m|Elle était cachée.
+maman|Tu la prends.
+maman|Avant de partir.
+papa|On reprend tes affaires.
+narrateur|Aniss prend l'affaire.
+papa|Bravo.
+papa|Tu as cherché.
+narrateur|Le livre reste sous le banc.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8627,7 +9108,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8791,7 +9272,7 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8819,7 +9300,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Un vélo passe au loin. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. La chaise frotte le carrelage. Dans le jardin, près de le livre, Aniss cherche. Près des pots, le seau est sale un peu. Il est un peu sale. On essuie le seau. Puis on part. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Les pots restent au jardin.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8959,7 +9440,24 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Un vélo passe au loin. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|La chaise frotte le carrelage.
+narrateur|Dans le jardin, près de le livre, Aniss cherche.
+narrateur|Près des pots, le seau est sale un peu.
+enfant-m|Il est un peu sale.
+papa|On essuie le seau.
+papa|Puis on part.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Les pots restent au jardin.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8987,7 +9485,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de le livre. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Les pots restent au jardin. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9127,7 +9625,19 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de le livre.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Les pots restent au jardin.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9155,7 +9665,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La lumière est claire. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Le tapis étouffe les pas. Dans le jardin, près de le livre, Aniss cherche. Sur la barrière, le manteau sèche. Il sèche, papa. Le manteau est presque sec. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. La barrière n'a plus le manteau.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9295,7 +9805,23 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. La lumière est claire. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Le tapis étouffe les pas.
+narrateur|Dans le jardin, près de le livre, Aniss cherche.
+narrateur|Sur la barrière, le manteau sèche.
+enfant-m|Il sèche, papa.
+maman|Le manteau est presque sec.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|La barrière n'a plus le manteau.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9323,7 +9849,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de le livre. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. La barrière n'a plus le manteau. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9463,7 +9989,19 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de le livre.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|La barrière n'a plus le manteau.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9491,7 +10029,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Ça sent le pain. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. Le seau tapote le sol. Dans le jardin, près de le livre, Aniss cherche. Dans l'herbe haute, le doudou. Il est dans l'herbe. Le doudou, tout doux. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. L'herbe haute est vide.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9631,7 +10169,23 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Ça sent le pain. Dans le jardin, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|Le seau tapote le sol.
+narrateur|Dans le jardin, près de le livre, Aniss cherche.
+narrateur|Dans l'herbe haute, le doudou.
+enfant-m|Il est dans l'herbe.
+papa|Le doudou, tout doux.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'herbe haute est vide.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9659,7 +10213,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de le livre. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. L'herbe haute est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9799,7 +10353,19 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de le livre.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'herbe haute est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9827,7 +10393,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans le jardin, Aniss s'approche de la dînette. Les tasses sont sur une planche. Le soleil chauffe un peu. Près de la dînette, il trouve encore une affaire. Je l'ai, maman. Tu la prends. Avant de partir. On reprend tes affaires. Aniss tient l'affaire. Bravo. La dînette reste au jardin.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9967,7 +10533,17 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans le jardin, Aniss s'approche de la dînette.
+narrateur|Les tasses sont sur une planche.
+narrateur|Le soleil chauffe un peu.
+narrateur|Près de la dînette, il trouve encore une affaire.
+enfant-m|Je l'ai, maman.
+maman|Tu la prends.
+maman|Avant de partir.
+papa|On reprend tes affaires.
+narrateur|Aniss tient l'affaire.
+maman|Bravo.
+narrateur|La dînette reste au jardin.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9995,7 +10571,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10159,7 +10735,7 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10187,7 +10763,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est claire. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Le crochet du manteau cliquette. Dans le jardin, près de la dînette, Aniss cherche. Au pied du cerisier, le seau. Près de l'arbre. Le seau près de l'arbre, oui. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le cerisier n'a plus le seau.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10327,7 +10903,23 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. La lumière est claire. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Le crochet du manteau cliquette.
+narrateur|Dans le jardin, près de la dînette, Aniss cherche.
+narrateur|Au pied du cerisier, le seau.
+enfant-m|Près de l'arbre.
+maman|Le seau près de l'arbre, oui.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le cerisier n'a plus le seau.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10355,7 +10947,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de la dînette. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le cerisier n'a plus le seau. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10495,7 +11087,19 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de la dînette.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le cerisier n'a plus le seau.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10523,7 +11127,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Ça sent le pain. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Le doudou glisse du canapé. Dans le jardin, près de la dînette, Aniss cherche. Sur le paillasson du jardin, le manteau. Sur le paillasson. Le manteau, tu le portes. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le paillasson n'a plus le manteau.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10663,7 +11267,23 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Ça sent le pain. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Le doudou glisse du canapé.
+narrateur|Dans le jardin, près de la dînette, Aniss cherche.
+narrateur|Sur le paillasson du jardin, le manteau.
+enfant-m|Sur le paillasson.
+papa|Le manteau, tu le portes.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le paillasson n'a plus le manteau.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10691,7 +11311,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de la dînette. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le paillasson n'a plus le manteau. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10831,7 +11451,19 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de la dînette.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le paillasson n'a plus le manteau.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10859,7 +11491,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Un chat miaule une fois. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. Les clés tintent dans le bol. Dans le jardin, près de la dînette, Aniss cherche. Dans la brouette, le doudou. Dans la brouette. La brouette reste. Le doudou vient. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. La brouette est vide.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10999,7 +11631,24 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Un chat miaule une fois. Dans le jardin, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|Les clés tintent dans le bol.
+narrateur|Dans le jardin, près de la dînette, Aniss cherche.
+narrateur|Dans la brouette, le doudou.
+enfant-m|Dans la brouette.
+maman|La brouette reste.
+maman|Le doudou vient.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|La brouette est vide.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11027,7 +11676,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans le jardin. Près de la dînette. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. La brouette est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11167,7 +11816,19 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans le jardin.
+narrateur|Près de la dînette.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|La brouette est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11195,7 +11856,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. On entend un oiseau. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir. Bravo.</t>
+          <t>Aniss va vers la chambre. Un oiseau chante derrière le volet. Le lit est défait. Il cherche près de l'oreiller. Il cherche sous le lit. Le doudou, papa ? Oui. On reprend tes affaires. Le seau. Le manteau. Le doudou. Avant de partir. Aniss trouve le doudou sous l'oreiller. Il le serre. Bravo, Aniss. Tu as cherché. Les autres affaires, tout à l'heure. Aniss tient le doudou. Il était là.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11335,8 +11996,25 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers la chambre. On entend un oiseau. Il cherche. Hugo reprend ses affaires. Le seau. Le manteau. Avant de partir.
-papa|Bravo.</t>
+          <t>narrateur|Aniss va vers la chambre.
+narrateur|Un oiseau chante derrière le volet.
+narrateur|Le lit est défait.
+narrateur|Il cherche près de l'oreiller.
+narrateur|Il cherche sous le lit.
+enfant-m|Le doudou, papa ?
+papa|Oui.
+papa|On reprend tes affaires.
+maman|Le seau.
+maman|Le manteau.
+maman|Le doudou.
+maman|Avant de partir.
+narrateur|Aniss trouve le doudou sous l'oreiller.
+narrateur|Il le serre.
+maman|Bravo, Aniss.
+maman|Tu as cherché.
+papa|Les autres affaires, tout à l'heure.
+narrateur|Aniss tient le doudou.
+enfant-m|Il était là.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11364,7 +12042,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Bientôt on part. Hugo fait quoi ?</t>
+          <t>Bientôt on part. Aniss fait quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11520,7 +12198,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Bientôt on part. Hugo fait quoi ?</t>
+          <t>narrateur|Bientôt on part.
+narrateur|Aniss fait quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11548,7 +12227,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+          <t>Oui. Aniss reprend ses affaires. Avant de partir. Il a cherché dans la chambre. Il a pris le doudou. Bravo. Tu as fait du bon travail. On continue avec papa. Oui.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11692,7 +12371,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Hugo reprend ses affaires. Avant de partir. On continue avec papa.</t>
+          <t>narrateur|Oui.
+papa|Aniss reprend ses affaires.
+maman|Avant de partir.
+narrateur|Il a cherché dans la chambre.
+narrateur|Il a pris le doudou.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|On continue avec papa.
+enfant-m|Oui.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11720,7 +12407,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Près des cubes, du livre, ou de la dînette ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11888,7 +12575,7 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Près des cubes, du livre, ou de la dînette ?</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11916,7 +12603,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans la chambre, Aniss s'approche des cubes. Une tour penche un peu. On entend un oiseau. Près des cubes, il trouve encore une affaire. Encore une. Oui. On reprend tes affaires. Avant de partir. Aniss met l'affaire près de lui. Bravo. Tu cherches bien. Les cubes restent au pied du lit.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12056,7 +12743,18 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Près des cubes, Hugo trouve encore une affaire. On entend un oiseau. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, Aniss s'approche des cubes.
+narrateur|Une tour penche un peu.
+narrateur|On entend un oiseau.
+narrateur|Près des cubes, il trouve encore une affaire.
+enfant-m|Encore une.
+papa|Oui.
+papa|On reprend tes affaires.
+maman|Avant de partir.
+narrateur|Aniss met l'affaire près de lui.
+papa|Bravo.
+papa|Tu cherches bien.
+narrateur|Les cubes restent au pied du lit.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12084,7 +12782,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12248,7 +12946,7 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12276,7 +12974,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Un vélo passe au loin. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Une miette roule sous la table. Dans la chambre, près de les cubes, Aniss cherche. Sous le lit, le seau a roulé. Sous le lit. Sous le lit, tu l'as vu. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Sous le lit, il n'y a plus le seau.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12416,7 +13114,23 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Un vélo passe au loin. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Une miette roule sous la table.
+narrateur|Dans la chambre, près de les cubes, Aniss cherche.
+narrateur|Sous le lit, le seau a roulé.
+enfant-m|Sous le lit.
+papa|Sous le lit, tu l'as vu.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Sous le lit, il n'y a plus le seau.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12444,7 +13158,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de les cubes. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Sous le lit, il n'y a plus le seau. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12584,7 +13298,19 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de les cubes.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Sous le lit, il n'y a plus le seau.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12612,7 +13338,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La lumière est claire. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Le vent pousse une feuille. Dans la chambre, près de les cubes, Aniss cherche. Sur le lit, le manteau est à plat. Sur le lit. Sur le lit, tu le prends. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le lit n'a plus le manteau.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12752,7 +13478,23 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. La lumière est claire. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Le vent pousse une feuille.
+narrateur|Dans la chambre, près de les cubes, Aniss cherche.
+narrateur|Sur le lit, le manteau est à plat.
+enfant-m|Sur le lit.
+maman|Sur le lit, tu le prends.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le lit n'a plus le manteau.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12780,7 +13522,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de les cubes. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le lit n'a plus le manteau. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12920,7 +13662,19 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de les cubes.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le lit n'a plus le manteau.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12948,7 +13702,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Ça sent le pain. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. La lampe fait un petit clic. Dans la chambre, près de les cubes, Aniss cherche. Sous l'oreiller, le doudou. Sous l'oreiller. Sous l'oreiller, tu l'as. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. L'oreiller est seul.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13088,7 +13842,23 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Ça sent le pain. Dans la chambre, près des cubes, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|La lampe fait un petit clic.
+narrateur|Dans la chambre, près de les cubes, Aniss cherche.
+narrateur|Sous l'oreiller, le doudou.
+enfant-m|Sous l'oreiller.
+papa|Sous l'oreiller, tu l'as.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'oreiller est seul.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13116,7 +13886,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de les cubes. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. L'oreiller est seul. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13256,7 +14026,19 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de les cubes.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|L'oreiller est seul.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13284,7 +14066,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans la chambre, Aniss s'approche du livre. Le livre est sur la commode. Ça sent l'herbe par la fenêtre ouverte. Près du livre, il trouve encore une affaire. Elle était sous le livre. Tu la prends. Avant de partir. On reprend tes affaires. Aniss prend l'affaire. Bravo. Le livre reste sur la commode.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13424,7 +14206,17 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Près du livre, Hugo trouve encore une affaire. Ça sent l'herbe coupée. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, Aniss s'approche du livre.
+narrateur|Le livre est sur la commode.
+narrateur|Ça sent l'herbe par la fenêtre ouverte.
+narrateur|Près du livre, il trouve encore une affaire.
+enfant-m|Elle était sous le livre.
+maman|Tu la prends.
+maman|Avant de partir.
+papa|On reprend tes affaires.
+narrateur|Aniss prend l'affaire.
+papa|Bravo.
+narrateur|Le livre reste sur la commode.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13452,7 +14244,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13616,7 +14408,7 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13644,7 +14436,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est claire. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Le paillasson est encore humide. Dans la chambre, près de le livre, Aniss cherche. Près de la commode, le seau. Près de la commode. Près de la commode, c'est bien. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. La commode est sage.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13784,7 +14576,23 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. La lumière est claire. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Le paillasson est encore humide.
+narrateur|Dans la chambre, près de le livre, Aniss cherche.
+narrateur|Près de la commode, le seau.
+enfant-m|Près de la commode.
+maman|Près de la commode, c'est bien.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|La commode est sage.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13812,7 +14620,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de le livre. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. La commode est sage. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13952,7 +14760,19 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de le livre.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|La commode est sage.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13980,7 +14800,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Ça sent le pain. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Un tiroir se ferme tout doux. Dans la chambre, près de le livre, Aniss cherche. Au pied du lit, le manteau. Au pied du lit. Au pied du lit, tu le prends. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le pied du lit est vide.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14120,7 +14940,23 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Ça sent le pain. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Un tiroir se ferme tout doux.
+narrateur|Dans la chambre, près de le livre, Aniss cherche.
+narrateur|Au pied du lit, le manteau.
+enfant-m|Au pied du lit.
+papa|Au pied du lit, tu le prends.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le pied du lit est vide.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14148,7 +14984,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de le livre. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le pied du lit est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14288,7 +15124,19 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de le livre.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le pied du lit est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14316,7 +15164,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Un chat miaule une fois. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. La page du livre frémit. Dans la chambre, près de le livre, Aniss cherche. Dans les draps, le doudou. Dans les draps. Dans les draps, tu l'as trouvé. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Les draps sont plats.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14456,7 +15304,23 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Un chat miaule une fois. Dans la chambre, près du livre, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|La page du livre frémit.
+narrateur|Dans la chambre, près de le livre, Aniss cherche.
+narrateur|Dans les draps, le doudou.
+enfant-m|Dans les draps.
+maman|Dans les draps, tu l'as trouvé.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Les draps sont plats.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14484,7 +15348,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de le livre. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Les draps sont plats. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14624,7 +15488,19 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de le livre.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Les draps sont plats.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14652,7 +15528,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>Dans la chambre, Aniss s'approche de la dînette. Les assiettes sont en bois. Le soleil chauffe un peu le tapis. Près de la dînette, il trouve encore une affaire. Je l'ai. Tu la prends. Avant de partir. On reprend tes affaires. Aniss serre l'affaire. Bravo. Tu as cherché. La dînette reste dans la chambre.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14792,7 +15668,18 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Près de la dînette, Hugo trouve encore une affaire. Le soleil chauffe un peu. Hugo reprend ses affaires. Avant de partir. maman n'est pas loin.</t>
+          <t>narrateur|Dans la chambre, Aniss s'approche de la dînette.
+narrateur|Les assiettes sont en bois.
+narrateur|Le soleil chauffe un peu le tapis.
+narrateur|Près de la dînette, il trouve encore une affaire.
+enfant-m|Je l'ai.
+maman|Tu la prends.
+maman|Avant de partir.
+papa|On reprend tes affaires.
+narrateur|Aniss serre l'affaire.
+maman|Bravo.
+maman|Tu as cherché.
+narrateur|La dînette reste dans la chambre.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14820,7 +15707,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14984,7 +15871,7 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est le matin, après la sieste, ou le soir ?</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15012,7 +15899,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Ça sent le pain. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>Le soleil est bas et doux. C'est le matin. On part ce matin. Une tasse de dînette tinte. Dans la chambre, près de la dînette, Aniss cherche. Derrière la porte, le seau. Derrière la porte. Derrière la porte, oui. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Derrière la porte, plus rien.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,7 +16039,23 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Ça sent le pain. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|Le soleil est bas et doux.
+narrateur|C'est le matin.
+papa|On part ce matin.
+narrateur|Une tasse de dînette tinte.
+narrateur|Dans la chambre, près de la dînette, Aniss cherche.
+narrateur|Derrière la porte, le seau.
+enfant-m|Derrière la porte.
+papa|Derrière la porte, oui.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Derrière la porte, plus rien.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15180,7 +16083,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de la dînette. C'était le matin. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Derrière la porte, plus rien. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,7 +16223,19 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de la dînette.
+narrateur|C'était le matin.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Derrière la porte, plus rien.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15348,7 +16263,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Un chat miaule une fois. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La maison est calme et tiède. C'est après la sieste. On part après la sieste. Le cube bleu tombe et s'arrête. Dans la chambre, près de la dînette, Aniss cherche. Sur le coffre, le manteau. Sur le coffre. Sur le coffre, tu le prends. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le coffre est fermé.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,7 +16403,23 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Un chat miaule une fois. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La maison est calme et tiède.
+narrateur|C'est après la sieste.
+maman|On part après la sieste.
+narrateur|Le cube bleu tombe et s'arrête.
+narrateur|Dans la chambre, près de la dînette, Aniss cherche.
+narrateur|Sur le coffre, le manteau.
+enfant-m|Sur le coffre.
+maman|Sur le coffre, tu le prends.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+papa|Merci, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|Le coffre est fermé.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15516,7 +16447,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de la dînette. C'était après la sieste. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le coffre est fermé. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,7 +16587,19 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de la dînette.
+narrateur|C'était après la sieste.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le coffre est fermé.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15684,7 +16627,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Une feuille tombe. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>La lampe fait une petite lumière. C'est le soir. On part ce soir. La porte de la cour craque. Dans la chambre, près de la dînette, Aniss cherche. Au bord du tapis, le doudou. Au bord du tapis. Au bord du tapis, bravo. Aniss prend le seau. Aniss prend le manteau. Aniss prend le doudou. Tu reprends tes affaires. Avant de partir. Aniss a tout. Merci, Aniss. Tu as fait du bon travail. Le tapis est vide.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,7 +16767,23 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Une feuille tombe. Dans la chambre, près de la dînette, Hugo a tout. Il reprend ses affaires. Avant de partir. Merci papa.</t>
+          <t>narrateur|La lampe fait une petite lumière.
+narrateur|C'est le soir.
+papa|On part ce soir.
+narrateur|La porte de la cour craque.
+narrateur|Dans la chambre, près de la dînette, Aniss cherche.
+narrateur|Au bord du tapis, le doudou.
+enfant-m|Au bord du tapis.
+papa|Au bord du tapis, bravo.
+narrateur|Aniss prend le seau.
+narrateur|Aniss prend le manteau.
+narrateur|Aniss prend le doudou.
+papa|Tu reprends tes affaires.
+maman|Avant de partir.
+narrateur|Aniss a tout.
+maman|Merci, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le tapis est vide.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15852,7 +16811,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a cherché dans la chambre. Près de la dînette. C'était le soir. J'ai le seau. J'ai le manteau. J'ai le doudou. Tu as repris tes affaires. Avant de partir. Bravo, Aniss. Tu as fait du bon travail. Le tapis est vide. La cour brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,7 +16951,19 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a cherché dans la chambre.
+narrateur|Près de la dînette.
+narrateur|C'était le soir.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+enfant-m|J'ai le doudou.
+papa|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le tapis est vide.
+narrateur|La cour brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16014,7 +16985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +17023,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
